--- a/user_inputs/terms.schema.xlsx
+++ b/user_inputs/terms.schema.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,8 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,6 +511,16 @@
           <t>Range (max)</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>GroupAfter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -563,6 +575,12 @@
           <t>3000</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Proof Pressure</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,11 +623,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ignition Temperature</t>
+          <t>Test Plan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -629,22 +649,20 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>K|degC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>5000</t>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>tpl-xxxx</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
         </is>
       </c>
     </row>
@@ -689,6 +707,11 @@
       <formula>$I2&lt;&gt;"number"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M2000">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>$C2="table(xy)"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"nearest,table(xy),line"</formula1>
@@ -710,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -813,6 +836,20 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Format: Optional value mask for string returns (e.g., tpl-xxxx) or /regex/ if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - GroupAfter: Only search values after this anchor text appears.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/user_inputs/terms.schema.xlsx
+++ b/user_inputs/terms.schema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
